--- a/docs/import-examples/05 Vendors and suppliers.xlsx
+++ b/docs/import-examples/05 Vendors and suppliers.xlsx
@@ -560,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F505"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -590,11 +590,106 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25"/>
@@ -889,312 +984,12 @@
     <row r="298" spans="2:2" x14ac:dyDescent="0.25"/>
     <row r="299" spans="2:2" x14ac:dyDescent="0.25"/>
     <row r="300" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="308" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="309" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="310" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="311" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="313" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="314" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="315" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="318" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="319" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="320" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="322" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="329" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="331" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="332" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="333" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="334" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="335" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="336" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="337" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="338" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="339" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="340" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="342" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="343" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="344" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="345" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="346" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="347" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="348" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="349" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="350" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="351" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="352" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="353" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="354" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="355" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="357" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="358" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="359" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="360" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="361" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="362" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="364" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="365" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="366" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="367" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="368" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="369" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="370" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="371" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="372" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="373" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="374" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="375" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="376" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="377" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="378" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="379" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="380" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="381" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="382" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="383" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="387" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="388" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="389" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="390" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="391" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="392" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="393" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="394" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="395" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="396" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="397" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="398" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="399" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="400" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="401" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="402" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="403" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="404" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="405" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="406" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="408" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="409" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="412" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="413" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="414" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="415" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="416" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="417" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="418" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="420" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="421" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="422" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="423" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="424" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="425" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="426" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="427" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="428" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="429" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="430" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="431" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="432" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="433" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="434" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="435" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="437" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="438" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="439" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="440" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="441" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="442" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="443" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="444" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="445" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="446" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="447" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="448" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="449" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="450" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="451" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="452" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="453" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="454" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="455" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="456" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="457" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="458" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="459" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="460" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="461" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="462" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="463" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="464" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="466" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="467" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="468" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="470" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="471" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="472" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="473" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="474" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="475" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="476" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="477" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="478" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="479" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="480" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="481" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="482" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="483" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="484" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="485" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="486" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="487" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="488" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="489" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="490" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="491" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="492" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="493" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="494" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="495" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="496" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="497" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="498" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="499" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="500" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
-        <v>6</v>
-      </c>
-      <c r="B501" t="s">
-        <v>7</v>
-      </c>
-      <c r="C501" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D501" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E501" t="s">
-        <v>10</v>
-      </c>
-      <c r="F501" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>12</v>
-      </c>
-      <c r="B502" t="s">
-        <v>7</v>
-      </c>
-      <c r="C502" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D502" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E502" t="s">
-        <v>15</v>
-      </c>
-      <c r="F502" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>17</v>
-      </c>
-      <c r="B503" t="s">
-        <v>7</v>
-      </c>
-      <c r="C503" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D503" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E503" t="s">
-        <v>20</v>
-      </c>
-      <c r="F503" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>22</v>
-      </c>
-      <c r="B504" t="s">
-        <v>23</v>
-      </c>
-      <c r="C504" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D504" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E504" t="s">
-        <v>26</v>
-      </c>
-      <c r="F504" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>28</v>
-      </c>
-      <c r="B505" t="s">
-        <v>29</v>
-      </c>
-      <c r="C505" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D505" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E505" t="s">
-        <v>31</v>
-      </c>
-      <c r="F505" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Raw material, Food agency, Rental, Transport, Labour, Decor, Hospitality" sqref="B10:B500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Raw material, Food agency, Rental, Transport, Labour, Decor, Hospitality" sqref="B10:B300">
       <formula1>"Raw material,Food agency,Rental,Transport,Labour,Decor,Hospitality"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Raw material, Food agency, Rental, Transport, Labour, Decor, Hospitality" sqref="B2:B500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Type" error="Choose one of: Raw material, Food agency, Rental, Transport, Labour, Decor, Hospitality" sqref="B2:B300">
       <formula1>"Raw material,Food agency,Rental,Transport,Labour,Decor,Hospitality"</formula1>
     </dataValidation>
   </dataValidations>
